--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.57388054552202</v>
+        <v>1.068255588647328</v>
       </c>
       <c r="D2" t="n">
-        <v>6.263317527720499</v>
+        <v>1.017789098254581</v>
       </c>
       <c r="E2" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F2" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.32938483201681</v>
+        <v>2.166025035202732</v>
       </c>
       <c r="D3" t="n">
-        <v>18.54516367420695</v>
+        <v>3.01358909705863</v>
       </c>
       <c r="E3" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F3" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.7900175162853</v>
+        <v>3.865877846396361</v>
       </c>
       <c r="D4" t="n">
-        <v>23.92982264203431</v>
+        <v>3.888596179330575</v>
       </c>
       <c r="E4" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F4" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.40000849184586</v>
+        <v>2.990001379924952</v>
       </c>
       <c r="D5" t="n">
-        <v>22.38387861148987</v>
+        <v>3.637380274367104</v>
       </c>
       <c r="E5" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F5" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.71078529153298</v>
+        <v>0.6030026098741091</v>
       </c>
       <c r="D6" t="n">
-        <v>3.711949687815348</v>
+        <v>0.6031918242699941</v>
       </c>
       <c r="E6" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F6" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.28079022434311</v>
+        <v>6.058128411455755</v>
       </c>
       <c r="D7" t="n">
-        <v>18.38901121459734</v>
+        <v>2.988214322372067</v>
       </c>
       <c r="E7" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F7" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.95752553798655</v>
+        <v>2.918097899922814</v>
       </c>
       <c r="D8" t="n">
-        <v>18.03712280451635</v>
+        <v>2.931032455733908</v>
       </c>
       <c r="E8" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F8" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.1348242124618</v>
+        <v>2.784408934525043</v>
       </c>
       <c r="D9" t="n">
-        <v>18.11767093199344</v>
+        <v>2.944121526448934</v>
       </c>
       <c r="E9" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F9" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.69676812009018</v>
+        <v>3.688224819514654</v>
       </c>
       <c r="D10" t="n">
-        <v>22.54369415520668</v>
+        <v>3.663350300221086</v>
       </c>
       <c r="E10" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F10" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.84846673259548</v>
+        <v>4.687875844046766</v>
       </c>
       <c r="D11" t="n">
-        <v>29.15670373538447</v>
+        <v>4.737964356999977</v>
       </c>
       <c r="E11" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F11" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>51.15372923099245</v>
+        <v>8.312481000036273</v>
       </c>
       <c r="D12" t="n">
-        <v>51.00419969297149</v>
+        <v>8.288182450107868</v>
       </c>
       <c r="E12" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F12" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.84810176450213</v>
+        <v>6.962816536731597</v>
       </c>
       <c r="D13" t="n">
-        <v>40.5979263510806</v>
+        <v>6.597163032050598</v>
       </c>
       <c r="E13" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F13" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>56.5350233133357</v>
+        <v>9.186941288417051</v>
       </c>
       <c r="D14" t="n">
-        <v>50.11319072465545</v>
+        <v>8.143393492756511</v>
       </c>
       <c r="E14" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F14" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>81.57357169493885</v>
+        <v>13.25570540042756</v>
       </c>
       <c r="D15" t="n">
-        <v>81.30637893085337</v>
+        <v>13.21228657626367</v>
       </c>
       <c r="E15" t="n">
-        <v>20.84877664688695</v>
+        <v>3.387926205119129</v>
       </c>
       <c r="F15" t="n">
-        <v>19.8715514863966</v>
+        <v>3.229127116539449</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
